--- a/Result/profitability/3037.xlsx
+++ b/Result/profitability/3037.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.73</v>
       </c>
       <c r="M2" t="n">
-        <v>1.13625</v>
+        <v>2.11</v>
       </c>
       <c r="N2" t="n">
-        <v>14.63375</v>
+        <v>15.78625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.6</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12875</v>
+        <v>2.18</v>
       </c>
       <c r="N3" t="n">
-        <v>14.21125</v>
+        <v>15.865</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.86</v>
       </c>
       <c r="M4" t="n">
-        <v>1.23125</v>
+        <v>2.2125</v>
       </c>
       <c r="N4" t="n">
-        <v>14.71625</v>
+        <v>16.14375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>1.165</v>
+        <v>2.21875</v>
       </c>
       <c r="N5" t="n">
-        <v>14.08375</v>
+        <v>15.54875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.16125</v>
+        <v>2.0375</v>
       </c>
       <c r="N6" t="n">
-        <v>13.16875</v>
+        <v>14.59625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.97</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1025</v>
+        <v>1.86875</v>
       </c>
       <c r="N7" t="n">
-        <v>13.7</v>
+        <v>14.82875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>1.23</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9662499999999999</v>
+        <v>1.6125</v>
       </c>
       <c r="N8" t="n">
-        <v>14.15</v>
+        <v>15.005</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1406,10 +1406,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>1.13</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6974999999999999</v>
+        <v>0.6975</v>
       </c>
       <c r="N9" t="n">
         <v>14.0925</v>
@@ -1899,7 +1899,7 @@
         <v>1.3</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8975</v>
+        <v>0.8975000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>15.81125</v>
@@ -2026,7 +2026,7 @@
         <v>0.83</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9924999999999999</v>
+        <v>0.9925</v>
       </c>
       <c r="N13" t="n">
         <v>16.5975</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>42890</v>
+      </c>
+      <c r="D75" t="n">
+        <v>32252</v>
+      </c>
+      <c r="E75" t="n">
+        <v>10638</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G75" t="n">
+        <v>6651</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.51%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>8925</v>
+      </c>
+      <c r="J75" t="n">
+        <v>15576</v>
+      </c>
+      <c r="K75" t="n">
+        <v>13115</v>
+      </c>
+      <c r="L75" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.10125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.576219512195122</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3808463251670378</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>421.4999999999999</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.8960244648318043</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
